--- a/uploadfile/pathdemy_list_upload.xlsx
+++ b/uploadfile/pathdemy_list_upload.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erice\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0-Python\2026ipuregreen\uploadfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B0DA23-86A8-4567-9578-9D1D02A24E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093C5463-BA65-42EE-B10F-C884A3870675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="學員清單" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Email(補課平台)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -32,6 +32,38 @@
   <si>
     <t>vinnyhuang168@gmail.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test001@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test002@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test003@gmail.com</t>
+  </si>
+  <si>
+    <t>test004@gmail.com</t>
+  </si>
+  <si>
+    <t>test005@gmail.com</t>
+  </si>
+  <si>
+    <t>test006@gmail.com</t>
+  </si>
+  <si>
+    <t>test007@gmail.com</t>
+  </si>
+  <si>
+    <t>test008@gmail.com</t>
+  </si>
+  <si>
+    <t>test009@gmail.com</t>
+  </si>
+  <si>
+    <t>test010@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -365,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBF661C-094A-4E26-8A03-54817ECA953B}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="25.21875" bestFit="1" customWidth="1"/>
@@ -388,6 +420,86 @@
         <v>46281.5</v>
       </c>
     </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4">
+        <v>46282.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46283.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4">
+        <v>46284.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46285.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46286.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46287.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46288.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4">
+        <v>46289.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46290.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46291.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/uploadfile/pathdemy_list_upload.xlsx
+++ b/uploadfile/pathdemy_list_upload.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093C5463-BA65-42EE-B10F-C884A3870675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="學員清單" sheetId="2" r:id="rId1"/>

--- a/uploadfile/pathdemy_list_upload.xlsx
+++ b/uploadfile/pathdemy_list_upload.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0-Python\2026ipuregreen\uploadfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093C5463-BA65-42EE-B10F-C884A3870675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52321D60-96F6-48FF-A6A3-A62A1F629C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="學員清單" sheetId="2" r:id="rId1"/>
+    <sheet name="補課名單" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
